--- a/ai_data.xlsx
+++ b/ai_data.xlsx
@@ -28,13 +28,14 @@
     <sheet name="productivity_growth" sheetId="19" r:id="rId19"/>
     <sheet name="gdp_per_capita" sheetId="20" r:id="rId20"/>
     <sheet name="infl" sheetId="21" r:id="rId21"/>
+    <sheet name="support" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11205" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11460" uniqueCount="582">
   <si>
     <t>country</t>
   </si>
@@ -1772,6 +1773,15 @@
   <si>
     <t>hicp_index</t>
   </si>
+  <si>
+    <t>state_aid_m_eur</t>
+  </si>
+  <si>
+    <t>gdp_m_eur</t>
+  </si>
+  <si>
+    <t>support_share</t>
+  </si>
 </sst>
 </file>
 
@@ -62275,6 +62285,4283 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E251"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>2000</v>
+      </c>
+      <c r="C2">
+        <v>465.1693401</v>
+      </c>
+      <c r="D2">
+        <v>212406.8</v>
+      </c>
+      <c r="E2">
+        <v>0.002189992693736736</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2001</v>
+      </c>
+      <c r="C3">
+        <v>651.7384922</v>
+      </c>
+      <c r="D3">
+        <v>219373.3</v>
+      </c>
+      <c r="E3">
+        <v>0.002970910736174366</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2002</v>
+      </c>
+      <c r="C4">
+        <v>789.4793999999999</v>
+      </c>
+      <c r="D4">
+        <v>225087.9</v>
+      </c>
+      <c r="E4">
+        <v>0.003507427098480194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2003</v>
+      </c>
+      <c r="C5">
+        <v>1122.8563</v>
+      </c>
+      <c r="D5">
+        <v>230541.9</v>
+      </c>
+      <c r="E5">
+        <v>0.004870508571326948</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>2004</v>
+      </c>
+      <c r="C6">
+        <v>1126.6842</v>
+      </c>
+      <c r="D6">
+        <v>240541.7</v>
+      </c>
+      <c r="E6">
+        <v>0.004683945444802295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2005</v>
+      </c>
+      <c r="C7">
+        <v>1129.5243</v>
+      </c>
+      <c r="D7">
+        <v>252354.9</v>
+      </c>
+      <c r="E7">
+        <v>0.004475935676303492</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>2006</v>
+      </c>
+      <c r="C8">
+        <v>1251.8298</v>
+      </c>
+      <c r="D8">
+        <v>265933.7</v>
+      </c>
+      <c r="E8">
+        <v>0.004707300353433957</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2007</v>
+      </c>
+      <c r="C9">
+        <v>1166.4323</v>
+      </c>
+      <c r="D9">
+        <v>282208.2</v>
+      </c>
+      <c r="E9">
+        <v>0.004133233194499663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>2008</v>
+      </c>
+      <c r="C10">
+        <v>1489.1082</v>
+      </c>
+      <c r="D10">
+        <v>291846.2</v>
+      </c>
+      <c r="E10">
+        <v>0.005102373099255703</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>2009</v>
+      </c>
+      <c r="C11">
+        <v>1725.3748</v>
+      </c>
+      <c r="D11">
+        <v>286274.1</v>
+      </c>
+      <c r="E11">
+        <v>0.006027002792079339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>2010</v>
+      </c>
+      <c r="C12">
+        <v>1920.9957</v>
+      </c>
+      <c r="D12">
+        <v>294050.6</v>
+      </c>
+      <c r="E12">
+        <v>0.006532874614097029</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>2011</v>
+      </c>
+      <c r="C13">
+        <v>1685.234</v>
+      </c>
+      <c r="D13">
+        <v>308167</v>
+      </c>
+      <c r="E13">
+        <v>0.005468573857681062</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>2012</v>
+      </c>
+      <c r="C14">
+        <v>1846.1894</v>
+      </c>
+      <c r="D14">
+        <v>316589.4</v>
+      </c>
+      <c r="E14">
+        <v>0.005831494674174182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>2013</v>
+      </c>
+      <c r="C15">
+        <v>1819.2337</v>
+      </c>
+      <c r="D15">
+        <v>321191.7</v>
+      </c>
+      <c r="E15">
+        <v>0.005664012177151526</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16">
+        <v>2014</v>
+      </c>
+      <c r="C16">
+        <v>1440.0815</v>
+      </c>
+      <c r="D16">
+        <v>330113.5</v>
+      </c>
+      <c r="E16">
+        <v>0.00436238293798951</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>2015</v>
+      </c>
+      <c r="C17">
+        <v>1876.5058</v>
+      </c>
+      <c r="D17">
+        <v>342083.5</v>
+      </c>
+      <c r="E17">
+        <v>0.005485519763449567</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>2016</v>
+      </c>
+      <c r="C18">
+        <v>1960.0512</v>
+      </c>
+      <c r="D18">
+        <v>355665.6</v>
+      </c>
+      <c r="E18">
+        <v>0.005510938364576163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2017</v>
+      </c>
+      <c r="C19">
+        <v>1889.5227</v>
+      </c>
+      <c r="D19">
+        <v>367294.9</v>
+      </c>
+      <c r="E19">
+        <v>0.0051444294489251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>2018</v>
+      </c>
+      <c r="C20">
+        <v>1864.7473</v>
+      </c>
+      <c r="D20">
+        <v>383234.3</v>
+      </c>
+      <c r="E20">
+        <v>0.00486581524670417</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>2019</v>
+      </c>
+      <c r="C21">
+        <v>1983.3662</v>
+      </c>
+      <c r="D21">
+        <v>395706.8</v>
+      </c>
+      <c r="E21">
+        <v>0.005012211566745884</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>2020</v>
+      </c>
+      <c r="C22">
+        <v>7965.9551</v>
+      </c>
+      <c r="D22">
+        <v>380317.9</v>
+      </c>
+      <c r="E22">
+        <v>0.02094551715814585</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>2021</v>
+      </c>
+      <c r="C23">
+        <v>9971.4764</v>
+      </c>
+      <c r="D23">
+        <v>406231.5</v>
+      </c>
+      <c r="E23">
+        <v>0.02454629047722788</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>2022</v>
+      </c>
+      <c r="C24">
+        <v>6330.031400000001</v>
+      </c>
+      <c r="D24">
+        <v>449382.2</v>
+      </c>
+      <c r="E24">
+        <v>0.0140860750603829</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>2023</v>
+      </c>
+      <c r="C25">
+        <v>3246.4424</v>
+      </c>
+      <c r="D25">
+        <v>477837.3</v>
+      </c>
+      <c r="E25">
+        <v>0.006794033031745324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>2024</v>
+      </c>
+      <c r="C26">
+        <v>3515.9482</v>
+      </c>
+      <c r="D26">
+        <v>494087.6</v>
+      </c>
+      <c r="E26">
+        <v>0.007116042175517054</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>2000</v>
+      </c>
+      <c r="C27">
+        <v>826.8256379000001</v>
+      </c>
+      <c r="D27">
+        <v>256376.4</v>
+      </c>
+      <c r="E27">
+        <v>0.003225045822860451</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>2001</v>
+      </c>
+      <c r="C28">
+        <v>824.4391666</v>
+      </c>
+      <c r="D28">
+        <v>264334.9</v>
+      </c>
+      <c r="E28">
+        <v>0.003118919093165526</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>2002</v>
+      </c>
+      <c r="C29">
+        <v>1035.3413</v>
+      </c>
+      <c r="D29">
+        <v>273255.9</v>
+      </c>
+      <c r="E29">
+        <v>0.003788907394131289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>2003</v>
+      </c>
+      <c r="C30">
+        <v>734.2064</v>
+      </c>
+      <c r="D30">
+        <v>281200.2</v>
+      </c>
+      <c r="E30">
+        <v>0.002610973960900455</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>2004</v>
+      </c>
+      <c r="C31">
+        <v>794.8402</v>
+      </c>
+      <c r="D31">
+        <v>296819.7</v>
+      </c>
+      <c r="E31">
+        <v>0.002677855277126147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>2005</v>
+      </c>
+      <c r="C32">
+        <v>823.9646</v>
+      </c>
+      <c r="D32">
+        <v>310037.6</v>
+      </c>
+      <c r="E32">
+        <v>0.002657627978025891</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>2006</v>
+      </c>
+      <c r="C33">
+        <v>1150.5343</v>
+      </c>
+      <c r="D33">
+        <v>325151.5</v>
+      </c>
+      <c r="E33">
+        <v>0.003538456073553405</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34">
+        <v>2007</v>
+      </c>
+      <c r="C34">
+        <v>1359.0867</v>
+      </c>
+      <c r="D34">
+        <v>343618.9</v>
+      </c>
+      <c r="E34">
+        <v>0.003955215210804761</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35">
+        <v>2008</v>
+      </c>
+      <c r="C35">
+        <v>1434.4233</v>
+      </c>
+      <c r="D35">
+        <v>351743.1</v>
+      </c>
+      <c r="E35">
+        <v>0.004078042469063359</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36">
+        <v>2009</v>
+      </c>
+      <c r="C36">
+        <v>2093.8646</v>
+      </c>
+      <c r="D36">
+        <v>347734.9</v>
+      </c>
+      <c r="E36">
+        <v>0.006021439320585882</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37">
+        <v>2010</v>
+      </c>
+      <c r="C37">
+        <v>2786.3809</v>
+      </c>
+      <c r="D37">
+        <v>363242.4</v>
+      </c>
+      <c r="E37">
+        <v>0.007670858082646739</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38">
+        <v>2011</v>
+      </c>
+      <c r="C38">
+        <v>2305.055</v>
+      </c>
+      <c r="D38">
+        <v>378745.4</v>
+      </c>
+      <c r="E38">
+        <v>0.006086027711491677</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39">
+        <v>2012</v>
+      </c>
+      <c r="C39">
+        <v>2058.64</v>
+      </c>
+      <c r="D39">
+        <v>387934.9</v>
+      </c>
+      <c r="E39">
+        <v>0.00530666356649015</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40">
+        <v>2013</v>
+      </c>
+      <c r="C40">
+        <v>2146.832</v>
+      </c>
+      <c r="D40">
+        <v>394616.3</v>
+      </c>
+      <c r="E40">
+        <v>0.005440302389941825</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41">
+        <v>2014</v>
+      </c>
+      <c r="C41">
+        <v>2238.1401</v>
+      </c>
+      <c r="D41">
+        <v>404958.3</v>
+      </c>
+      <c r="E41">
+        <v>0.005526840911767953</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42">
+        <v>2015</v>
+      </c>
+      <c r="C42">
+        <v>2161.9513</v>
+      </c>
+      <c r="D42">
+        <v>415538</v>
+      </c>
+      <c r="E42">
+        <v>0.005202776400714255</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43">
+        <v>2016</v>
+      </c>
+      <c r="C43">
+        <v>2611.6519</v>
+      </c>
+      <c r="D43">
+        <v>428467.1</v>
+      </c>
+      <c r="E43">
+        <v>0.006095338241839338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44">
+        <v>2017</v>
+      </c>
+      <c r="C44">
+        <v>2180.9069</v>
+      </c>
+      <c r="D44">
+        <v>443407.2</v>
+      </c>
+      <c r="E44">
+        <v>0.004918519365495193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45">
+        <v>2018</v>
+      </c>
+      <c r="C45">
+        <v>3514.3988</v>
+      </c>
+      <c r="D45">
+        <v>459491.8</v>
+      </c>
+      <c r="E45">
+        <v>0.007648447262823842</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46">
+        <v>2019</v>
+      </c>
+      <c r="C46">
+        <v>4490.8162</v>
+      </c>
+      <c r="D46">
+        <v>479444.9</v>
+      </c>
+      <c r="E46">
+        <v>0.00936669928077241</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>2020</v>
+      </c>
+      <c r="C47">
+        <v>6357.639</v>
+      </c>
+      <c r="D47">
+        <v>463750.9</v>
+      </c>
+      <c r="E47">
+        <v>0.01370916800377099</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2021</v>
+      </c>
+      <c r="C48">
+        <v>6150.624</v>
+      </c>
+      <c r="D48">
+        <v>506047.2</v>
+      </c>
+      <c r="E48">
+        <v>0.01215424964311629</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>2022</v>
+      </c>
+      <c r="C49">
+        <v>5534.2528</v>
+      </c>
+      <c r="D49">
+        <v>561678.2</v>
+      </c>
+      <c r="E49">
+        <v>0.009853066756017948</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>2023</v>
+      </c>
+      <c r="C50">
+        <v>5509.4958</v>
+      </c>
+      <c r="D50">
+        <v>601866.5</v>
+      </c>
+      <c r="E50">
+        <v>0.00915401638070901</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>2024</v>
+      </c>
+      <c r="C51">
+        <v>6197.9128</v>
+      </c>
+      <c r="D51">
+        <v>619914.3</v>
+      </c>
+      <c r="E51">
+        <v>0.009998015532146944</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52">
+        <v>2000</v>
+      </c>
+      <c r="C52">
+        <v>14649.326186</v>
+      </c>
+      <c r="D52">
+        <v>2129660</v>
+      </c>
+      <c r="E52">
+        <v>0.00687871593869444</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53">
+        <v>2001</v>
+      </c>
+      <c r="C53">
+        <v>15371.3117363</v>
+      </c>
+      <c r="D53">
+        <v>2195530</v>
+      </c>
+      <c r="E53">
+        <v>0.007001185015144407</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54">
+        <v>2002</v>
+      </c>
+      <c r="C54">
+        <v>20232.8742</v>
+      </c>
+      <c r="D54">
+        <v>2223360</v>
+      </c>
+      <c r="E54">
+        <v>0.009100134121329878</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55">
+        <v>2003</v>
+      </c>
+      <c r="C55">
+        <v>19558.6731</v>
+      </c>
+      <c r="D55">
+        <v>2240810</v>
+      </c>
+      <c r="E55">
+        <v>0.008728394241368077</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56">
+        <v>2004</v>
+      </c>
+      <c r="C56">
+        <v>16785.0716</v>
+      </c>
+      <c r="D56">
+        <v>2293040</v>
+      </c>
+      <c r="E56">
+        <v>0.007320008198723092</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57">
+        <v>2005</v>
+      </c>
+      <c r="C57">
+        <v>16757.725</v>
+      </c>
+      <c r="D57">
+        <v>2325710</v>
+      </c>
+      <c r="E57">
+        <v>0.007205423290092057</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58">
+        <v>2006</v>
+      </c>
+      <c r="C58">
+        <v>17906.2518</v>
+      </c>
+      <c r="D58">
+        <v>2426180</v>
+      </c>
+      <c r="E58">
+        <v>0.007380430058775525</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59">
+        <v>2007</v>
+      </c>
+      <c r="C59">
+        <v>14569.9035</v>
+      </c>
+      <c r="D59">
+        <v>2542220</v>
+      </c>
+      <c r="E59">
+        <v>0.00573117334455712</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60">
+        <v>2008</v>
+      </c>
+      <c r="C60">
+        <v>15971.6008</v>
+      </c>
+      <c r="D60">
+        <v>2589280</v>
+      </c>
+      <c r="E60">
+        <v>0.006168355990854601</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61">
+        <v>2009</v>
+      </c>
+      <c r="C61">
+        <v>16481.7426</v>
+      </c>
+      <c r="D61">
+        <v>2493970</v>
+      </c>
+      <c r="E61">
+        <v>0.006608637072619158</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>2010</v>
+      </c>
+      <c r="C62">
+        <v>13446.9247</v>
+      </c>
+      <c r="D62">
+        <v>2615260</v>
+      </c>
+      <c r="E62">
+        <v>0.005141716196477597</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2011</v>
+      </c>
+      <c r="C63">
+        <v>11691.003</v>
+      </c>
+      <c r="D63">
+        <v>2747210</v>
+      </c>
+      <c r="E63">
+        <v>0.004255591309000768</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>2012</v>
+      </c>
+      <c r="C64">
+        <v>11345.668</v>
+      </c>
+      <c r="D64">
+        <v>2800680</v>
+      </c>
+      <c r="E64">
+        <v>0.004051040461602182</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>2013</v>
+      </c>
+      <c r="C65">
+        <v>12014.7465</v>
+      </c>
+      <c r="D65">
+        <v>2869480</v>
+      </c>
+      <c r="E65">
+        <v>0.004187081457267519</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>2014</v>
+      </c>
+      <c r="C66">
+        <v>31016.8113</v>
+      </c>
+      <c r="D66">
+        <v>2988470</v>
+      </c>
+      <c r="E66">
+        <v>0.01037882638942335</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>2015</v>
+      </c>
+      <c r="C67">
+        <v>35160.3166</v>
+      </c>
+      <c r="D67">
+        <v>3094190</v>
+      </c>
+      <c r="E67">
+        <v>0.01136333470148892</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>2016</v>
+      </c>
+      <c r="C68">
+        <v>39692.5269</v>
+      </c>
+      <c r="D68">
+        <v>3204870</v>
+      </c>
+      <c r="E68">
+        <v>0.01238506613372773</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>2017</v>
+      </c>
+      <c r="C69">
+        <v>41977.0361</v>
+      </c>
+      <c r="D69">
+        <v>3345860</v>
+      </c>
+      <c r="E69">
+        <v>0.01254596310066769</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>2018</v>
+      </c>
+      <c r="C70">
+        <v>45406.4451</v>
+      </c>
+      <c r="D70">
+        <v>3450580</v>
+      </c>
+      <c r="E70">
+        <v>0.01315907618429366</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>2019</v>
+      </c>
+      <c r="C71">
+        <v>45824.7516</v>
+      </c>
+      <c r="D71">
+        <v>3557630</v>
+      </c>
+      <c r="E71">
+        <v>0.01288069630624882</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>2020</v>
+      </c>
+      <c r="C72">
+        <v>120184.444</v>
+      </c>
+      <c r="D72">
+        <v>3477670</v>
+      </c>
+      <c r="E72">
+        <v>0.03455889834285599</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>2021</v>
+      </c>
+      <c r="C73">
+        <v>102019.7943</v>
+      </c>
+      <c r="D73">
+        <v>3713090</v>
+      </c>
+      <c r="E73">
+        <v>0.02747571276214689</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>2022</v>
+      </c>
+      <c r="C74">
+        <v>53990.6493</v>
+      </c>
+      <c r="D74">
+        <v>4010630</v>
+      </c>
+      <c r="E74">
+        <v>0.01346188735934255</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>2023</v>
+      </c>
+      <c r="C75">
+        <v>46651.3509</v>
+      </c>
+      <c r="D75">
+        <v>4254930</v>
+      </c>
+      <c r="E75">
+        <v>0.010964070125713</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>2024</v>
+      </c>
+      <c r="C76">
+        <v>36846.9003</v>
+      </c>
+      <c r="D76">
+        <v>4386940</v>
+      </c>
+      <c r="E76">
+        <v>0.008399225952486244</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>2000</v>
+      </c>
+      <c r="C77">
+        <v>3510.2834032</v>
+      </c>
+      <c r="D77">
+        <v>647569</v>
+      </c>
+      <c r="E77">
+        <v>0.005420709458297108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2001</v>
+      </c>
+      <c r="C78">
+        <v>4346.305288799999</v>
+      </c>
+      <c r="D78">
+        <v>700958</v>
+      </c>
+      <c r="E78">
+        <v>0.006200521698589643</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>2002</v>
+      </c>
+      <c r="C79">
+        <v>4302.8211</v>
+      </c>
+      <c r="D79">
+        <v>749744</v>
+      </c>
+      <c r="E79">
+        <v>0.005739053730339956</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>2003</v>
+      </c>
+      <c r="C80">
+        <v>4204.6289</v>
+      </c>
+      <c r="D80">
+        <v>802683</v>
+      </c>
+      <c r="E80">
+        <v>0.005238218449873736</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>2004</v>
+      </c>
+      <c r="C81">
+        <v>3807.1346</v>
+      </c>
+      <c r="D81">
+        <v>860059</v>
+      </c>
+      <c r="E81">
+        <v>0.004426597012530536</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>2005</v>
+      </c>
+      <c r="C82">
+        <v>4208.5796</v>
+      </c>
+      <c r="D82">
+        <v>928122</v>
+      </c>
+      <c r="E82">
+        <v>0.004534511195726424</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>2006</v>
+      </c>
+      <c r="C83">
+        <v>4766.853599999999</v>
+      </c>
+      <c r="D83">
+        <v>1004976</v>
+      </c>
+      <c r="E83">
+        <v>0.004743251182117781</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>2007</v>
+      </c>
+      <c r="C84">
+        <v>4854.5349</v>
+      </c>
+      <c r="D84">
+        <v>1077541</v>
+      </c>
+      <c r="E84">
+        <v>0.004505197389240873</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>2008</v>
+      </c>
+      <c r="C85">
+        <v>5546.3774</v>
+      </c>
+      <c r="D85">
+        <v>1112432</v>
+      </c>
+      <c r="E85">
+        <v>0.00498581252606901</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>2009</v>
+      </c>
+      <c r="C86">
+        <v>5468.6737</v>
+      </c>
+      <c r="D86">
+        <v>1072990</v>
+      </c>
+      <c r="E86">
+        <v>0.00509666790930018</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>2010</v>
+      </c>
+      <c r="C87">
+        <v>4811.5833</v>
+      </c>
+      <c r="D87">
+        <v>1077145</v>
+      </c>
+      <c r="E87">
+        <v>0.004466978261979586</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>2011</v>
+      </c>
+      <c r="C88">
+        <v>4427.693</v>
+      </c>
+      <c r="D88">
+        <v>1068690</v>
+      </c>
+      <c r="E88">
+        <v>0.004143103238544386</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>2012</v>
+      </c>
+      <c r="C89">
+        <v>3862.528</v>
+      </c>
+      <c r="D89">
+        <v>1035964</v>
+      </c>
+      <c r="E89">
+        <v>0.00372843843994579</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>2013</v>
+      </c>
+      <c r="C90">
+        <v>3031.52</v>
+      </c>
+      <c r="D90">
+        <v>1025652</v>
+      </c>
+      <c r="E90">
+        <v>0.002955700374005998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>2014</v>
+      </c>
+      <c r="C91">
+        <v>3348.06</v>
+      </c>
+      <c r="D91">
+        <v>1038949</v>
+      </c>
+      <c r="E91">
+        <v>0.003222545091241245</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92">
+        <v>2015</v>
+      </c>
+      <c r="C92">
+        <v>2860.6436</v>
+      </c>
+      <c r="D92">
+        <v>1087112</v>
+      </c>
+      <c r="E92">
+        <v>0.002631415714296227</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93">
+        <v>2016</v>
+      </c>
+      <c r="C93">
+        <v>9247.1582</v>
+      </c>
+      <c r="D93">
+        <v>1122967</v>
+      </c>
+      <c r="E93">
+        <v>0.008234576973321566</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94">
+        <v>2017</v>
+      </c>
+      <c r="C94">
+        <v>9910.049499999999</v>
+      </c>
+      <c r="D94">
+        <v>1170024</v>
+      </c>
+      <c r="E94">
+        <v>0.008469954035130903</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95">
+        <v>2018</v>
+      </c>
+      <c r="C95">
+        <v>10971.8912</v>
+      </c>
+      <c r="D95">
+        <v>1212276</v>
+      </c>
+      <c r="E95">
+        <v>0.009050654471423999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96">
+        <v>2019</v>
+      </c>
+      <c r="C96">
+        <v>11847.1257</v>
+      </c>
+      <c r="D96">
+        <v>1253710</v>
+      </c>
+      <c r="E96">
+        <v>0.009449653986966683</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97">
+        <v>2020</v>
+      </c>
+      <c r="C97">
+        <v>15156.4574</v>
+      </c>
+      <c r="D97">
+        <v>1129214</v>
+      </c>
+      <c r="E97">
+        <v>0.01342213026051749</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>6</v>
+      </c>
+      <c r="B98">
+        <v>2021</v>
+      </c>
+      <c r="C98">
+        <v>19289.3189</v>
+      </c>
+      <c r="D98">
+        <v>1235474</v>
+      </c>
+      <c r="E98">
+        <v>0.0156128893849648</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99">
+        <v>2022</v>
+      </c>
+      <c r="C99">
+        <v>13947.9437</v>
+      </c>
+      <c r="D99">
+        <v>1375863</v>
+      </c>
+      <c r="E99">
+        <v>0.0101375963304486</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100">
+        <v>2023</v>
+      </c>
+      <c r="C100">
+        <v>16224.8618</v>
+      </c>
+      <c r="D100">
+        <v>1497761</v>
+      </c>
+      <c r="E100">
+        <v>0.01083274420952341</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101">
+        <v>2024</v>
+      </c>
+      <c r="C101">
+        <v>15542.712</v>
+      </c>
+      <c r="D101">
+        <v>1594330</v>
+      </c>
+      <c r="E101">
+        <v>0.009748742104834006</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>7</v>
+      </c>
+      <c r="B102">
+        <v>2000</v>
+      </c>
+      <c r="C102">
+        <v>481.0072529999999</v>
+      </c>
+      <c r="D102">
+        <v>136386</v>
+      </c>
+      <c r="E102">
+        <v>0.003526808125467423</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>7</v>
+      </c>
+      <c r="B103">
+        <v>2001</v>
+      </c>
+      <c r="C103">
+        <v>435.1742686</v>
+      </c>
+      <c r="D103">
+        <v>144613</v>
+      </c>
+      <c r="E103">
+        <v>0.003009233392571899</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>7</v>
+      </c>
+      <c r="B104">
+        <v>2002</v>
+      </c>
+      <c r="C104">
+        <v>968.9136000000001</v>
+      </c>
+      <c r="D104">
+        <v>148440</v>
+      </c>
+      <c r="E104">
+        <v>0.00652730800323363</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>7</v>
+      </c>
+      <c r="B105">
+        <v>2003</v>
+      </c>
+      <c r="C105">
+        <v>1086.4643</v>
+      </c>
+      <c r="D105">
+        <v>151714</v>
+      </c>
+      <c r="E105">
+        <v>0.007161265934587446</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>7</v>
+      </c>
+      <c r="B106">
+        <v>2004</v>
+      </c>
+      <c r="C106">
+        <v>1146.8758</v>
+      </c>
+      <c r="D106">
+        <v>158741</v>
+      </c>
+      <c r="E106">
+        <v>0.007224824084515028</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107">
+        <v>2005</v>
+      </c>
+      <c r="C107">
+        <v>1353.8122</v>
+      </c>
+      <c r="D107">
+        <v>164666</v>
+      </c>
+      <c r="E107">
+        <v>0.008221564864635079</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>7</v>
+      </c>
+      <c r="B108">
+        <v>2006</v>
+      </c>
+      <c r="C108">
+        <v>1358.4025</v>
+      </c>
+      <c r="D108">
+        <v>172861</v>
+      </c>
+      <c r="E108">
+        <v>0.007858351507858916</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>7</v>
+      </c>
+      <c r="B109">
+        <v>2007</v>
+      </c>
+      <c r="C109">
+        <v>1308.5504</v>
+      </c>
+      <c r="D109">
+        <v>187059</v>
+      </c>
+      <c r="E109">
+        <v>0.00699538862070256</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>7</v>
+      </c>
+      <c r="B110">
+        <v>2008</v>
+      </c>
+      <c r="C110">
+        <v>1207.217</v>
+      </c>
+      <c r="D110">
+        <v>194253</v>
+      </c>
+      <c r="E110">
+        <v>0.006214663351402553</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>7</v>
+      </c>
+      <c r="B111">
+        <v>2009</v>
+      </c>
+      <c r="C111">
+        <v>1237.9112</v>
+      </c>
+      <c r="D111">
+        <v>181735</v>
+      </c>
+      <c r="E111">
+        <v>0.006811627919773296</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>7</v>
+      </c>
+      <c r="B112">
+        <v>2010</v>
+      </c>
+      <c r="C112">
+        <v>2074.6611</v>
+      </c>
+      <c r="D112">
+        <v>188147</v>
+      </c>
+      <c r="E112">
+        <v>0.01102680935651379</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>7</v>
+      </c>
+      <c r="B113">
+        <v>2011</v>
+      </c>
+      <c r="C113">
+        <v>2840.529</v>
+      </c>
+      <c r="D113">
+        <v>197655</v>
+      </c>
+      <c r="E113">
+        <v>0.01437114669499886</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>7</v>
+      </c>
+      <c r="B114">
+        <v>2012</v>
+      </c>
+      <c r="C114">
+        <v>2331.2</v>
+      </c>
+      <c r="D114">
+        <v>200378</v>
+      </c>
+      <c r="E114">
+        <v>0.01163401171785326</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115">
+        <v>2013</v>
+      </c>
+      <c r="C115">
+        <v>2446.8</v>
+      </c>
+      <c r="D115">
+        <v>203497</v>
+      </c>
+      <c r="E115">
+        <v>0.01202376447810041</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B116">
+        <v>2014</v>
+      </c>
+      <c r="C116">
+        <v>2512.601</v>
+      </c>
+      <c r="D116">
+        <v>205855</v>
+      </c>
+      <c r="E116">
+        <v>0.01220568361225134</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>7</v>
+      </c>
+      <c r="B117">
+        <v>2015</v>
+      </c>
+      <c r="C117">
+        <v>2244.68</v>
+      </c>
+      <c r="D117">
+        <v>210192</v>
+      </c>
+      <c r="E117">
+        <v>0.01067918855141965</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>7</v>
+      </c>
+      <c r="B118">
+        <v>2016</v>
+      </c>
+      <c r="C118">
+        <v>1963.319</v>
+      </c>
+      <c r="D118">
+        <v>215717</v>
+      </c>
+      <c r="E118">
+        <v>0.00910136428746923</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119">
+        <v>2017</v>
+      </c>
+      <c r="C119">
+        <v>2145.944</v>
+      </c>
+      <c r="D119">
+        <v>224706</v>
+      </c>
+      <c r="E119">
+        <v>0.009550007565441065</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>7</v>
+      </c>
+      <c r="B120">
+        <v>2018</v>
+      </c>
+      <c r="C120">
+        <v>2261.838</v>
+      </c>
+      <c r="D120">
+        <v>231905</v>
+      </c>
+      <c r="E120">
+        <v>0.009753295530497403</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>7</v>
+      </c>
+      <c r="B121">
+        <v>2019</v>
+      </c>
+      <c r="C121">
+        <v>2180.927</v>
+      </c>
+      <c r="D121">
+        <v>238518</v>
+      </c>
+      <c r="E121">
+        <v>0.009143657920995481</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>7</v>
+      </c>
+      <c r="B122">
+        <v>2020</v>
+      </c>
+      <c r="C122">
+        <v>2744.7407</v>
+      </c>
+      <c r="D122">
+        <v>236387</v>
+      </c>
+      <c r="E122">
+        <v>0.01161121677588023</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>7</v>
+      </c>
+      <c r="B123">
+        <v>2021</v>
+      </c>
+      <c r="C123">
+        <v>3608.4422</v>
+      </c>
+      <c r="D123">
+        <v>248764</v>
+      </c>
+      <c r="E123">
+        <v>0.01450548391246322</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>7</v>
+      </c>
+      <c r="B124">
+        <v>2022</v>
+      </c>
+      <c r="C124">
+        <v>2460.5379</v>
+      </c>
+      <c r="D124">
+        <v>265669</v>
+      </c>
+      <c r="E124">
+        <v>0.009261667337928024</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>7</v>
+      </c>
+      <c r="B125">
+        <v>2023</v>
+      </c>
+      <c r="C125">
+        <v>2827.7081</v>
+      </c>
+      <c r="D125">
+        <v>272735</v>
+      </c>
+      <c r="E125">
+        <v>0.0103679692742039</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>7</v>
+      </c>
+      <c r="B126">
+        <v>2024</v>
+      </c>
+      <c r="C126">
+        <v>2276.9933</v>
+      </c>
+      <c r="D126">
+        <v>276151</v>
+      </c>
+      <c r="E126">
+        <v>0.008245464618994681</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127">
+        <v>2000</v>
+      </c>
+      <c r="C127">
+        <v>5237.0975824</v>
+      </c>
+      <c r="D127">
+        <v>1473517.3</v>
+      </c>
+      <c r="E127">
+        <v>0.003554147333322791</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>8</v>
+      </c>
+      <c r="B128">
+        <v>2001</v>
+      </c>
+      <c r="C128">
+        <v>4812.7275465</v>
+      </c>
+      <c r="D128">
+        <v>1530070.9</v>
+      </c>
+      <c r="E128">
+        <v>0.003145427801090786</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129">
+        <v>2002</v>
+      </c>
+      <c r="C129">
+        <v>6807.8169</v>
+      </c>
+      <c r="D129">
+        <v>1578330.4</v>
+      </c>
+      <c r="E129">
+        <v>0.004313302778683094</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130">
+        <v>2003</v>
+      </c>
+      <c r="C130">
+        <v>7075.8806</v>
+      </c>
+      <c r="D130">
+        <v>1622312.8</v>
+      </c>
+      <c r="E130">
+        <v>0.004361600672817227</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131">
+        <v>2004</v>
+      </c>
+      <c r="C131">
+        <v>7601.256</v>
+      </c>
+      <c r="D131">
+        <v>1696107.7</v>
+      </c>
+      <c r="E131">
+        <v>0.00448158805009847</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132">
+        <v>2005</v>
+      </c>
+      <c r="C132">
+        <v>7995.0689</v>
+      </c>
+      <c r="D132">
+        <v>1762047.7</v>
+      </c>
+      <c r="E132">
+        <v>0.004537373704468954</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133">
+        <v>2006</v>
+      </c>
+      <c r="C133">
+        <v>8963.241599999999</v>
+      </c>
+      <c r="D133">
+        <v>1846020.8</v>
+      </c>
+      <c r="E133">
+        <v>0.004855439115312243</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134">
+        <v>2007</v>
+      </c>
+      <c r="C134">
+        <v>8435.8871</v>
+      </c>
+      <c r="D134">
+        <v>1937876.3</v>
+      </c>
+      <c r="E134">
+        <v>0.004353160777083656</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>8</v>
+      </c>
+      <c r="B135">
+        <v>2008</v>
+      </c>
+      <c r="C135">
+        <v>11414.9058</v>
+      </c>
+      <c r="D135">
+        <v>1989999.7</v>
+      </c>
+      <c r="E135">
+        <v>0.005736134432583081</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136">
+        <v>2009</v>
+      </c>
+      <c r="C136">
+        <v>12918.7955</v>
+      </c>
+      <c r="D136">
+        <v>1935840.2</v>
+      </c>
+      <c r="E136">
+        <v>0.006673482397978925</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137">
+        <v>2010</v>
+      </c>
+      <c r="C137">
+        <v>13306.8608</v>
+      </c>
+      <c r="D137">
+        <v>1996075.1</v>
+      </c>
+      <c r="E137">
+        <v>0.006666513098630407</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138">
+        <v>2011</v>
+      </c>
+      <c r="C138">
+        <v>10915.602</v>
+      </c>
+      <c r="D138">
+        <v>2062141.4</v>
+      </c>
+      <c r="E138">
+        <v>0.005293333425147278</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139">
+        <v>2012</v>
+      </c>
+      <c r="C139">
+        <v>11011.634</v>
+      </c>
+      <c r="D139">
+        <v>2088286.7</v>
+      </c>
+      <c r="E139">
+        <v>0.005273047038991342</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140">
+        <v>2013</v>
+      </c>
+      <c r="C140">
+        <v>9481.040000000001</v>
+      </c>
+      <c r="D140">
+        <v>2120351.9</v>
+      </c>
+      <c r="E140">
+        <v>0.004471446461316162</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141">
+        <v>2014</v>
+      </c>
+      <c r="C141">
+        <v>11371.6482</v>
+      </c>
+      <c r="D141">
+        <v>2153733.1</v>
+      </c>
+      <c r="E141">
+        <v>0.005279970949046565</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142">
+        <v>2015</v>
+      </c>
+      <c r="C142">
+        <v>11908.9099</v>
+      </c>
+      <c r="D142">
+        <v>2201401.6</v>
+      </c>
+      <c r="E142">
+        <v>0.005409694396515384</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143">
+        <v>2016</v>
+      </c>
+      <c r="C143">
+        <v>11181.9925</v>
+      </c>
+      <c r="D143">
+        <v>2231819.2</v>
+      </c>
+      <c r="E143">
+        <v>0.005010259119555921</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144">
+        <v>2017</v>
+      </c>
+      <c r="C144">
+        <v>13174.0314</v>
+      </c>
+      <c r="D144">
+        <v>2291680.5</v>
+      </c>
+      <c r="E144">
+        <v>0.005748633546430229</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145">
+        <v>2018</v>
+      </c>
+      <c r="C145">
+        <v>16642.5098</v>
+      </c>
+      <c r="D145">
+        <v>2355362.8</v>
+      </c>
+      <c r="E145">
+        <v>0.007065794619835212</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146">
+        <v>2019</v>
+      </c>
+      <c r="C146">
+        <v>16238.2453</v>
+      </c>
+      <c r="D146">
+        <v>2432206.8</v>
+      </c>
+      <c r="E146">
+        <v>0.006676342365295583</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147">
+        <v>2020</v>
+      </c>
+      <c r="C147">
+        <v>43983.5033</v>
+      </c>
+      <c r="D147">
+        <v>2318276.2</v>
+      </c>
+      <c r="E147">
+        <v>0.0189725034920343</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148">
+        <v>2021</v>
+      </c>
+      <c r="C148">
+        <v>54992.2694</v>
+      </c>
+      <c r="D148">
+        <v>2508102.3</v>
+      </c>
+      <c r="E148">
+        <v>0.02192584784121445</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149">
+        <v>2022</v>
+      </c>
+      <c r="C149">
+        <v>33789.7223</v>
+      </c>
+      <c r="D149">
+        <v>2653997.2</v>
+      </c>
+      <c r="E149">
+        <v>0.0127316344945654</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150">
+        <v>2023</v>
+      </c>
+      <c r="C150">
+        <v>29342.5955</v>
+      </c>
+      <c r="D150">
+        <v>2833826.4</v>
+      </c>
+      <c r="E150">
+        <v>0.0103544082657992</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151">
+        <v>2024</v>
+      </c>
+      <c r="C151">
+        <v>24898.4924</v>
+      </c>
+      <c r="D151">
+        <v>2935236.2</v>
+      </c>
+      <c r="E151">
+        <v>0.008482619695137311</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152">
+        <v>2000</v>
+      </c>
+      <c r="C152">
+        <v>580.5412</v>
+      </c>
+      <c r="D152">
+        <v>108495.3</v>
+      </c>
+      <c r="E152">
+        <v>0.005350841925871443</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153">
+        <v>2001</v>
+      </c>
+      <c r="C153">
+        <v>611.1643</v>
+      </c>
+      <c r="D153">
+        <v>122089.2</v>
+      </c>
+      <c r="E153">
+        <v>0.005005883403282191</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154">
+        <v>2002</v>
+      </c>
+      <c r="C154">
+        <v>644.4208</v>
+      </c>
+      <c r="D154">
+        <v>135997.9</v>
+      </c>
+      <c r="E154">
+        <v>0.004738461402712836</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155">
+        <v>2003</v>
+      </c>
+      <c r="C155">
+        <v>486.402</v>
+      </c>
+      <c r="D155">
+        <v>145576.9</v>
+      </c>
+      <c r="E155">
+        <v>0.003341203171657042</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156">
+        <v>2004</v>
+      </c>
+      <c r="C156">
+        <v>500.7845</v>
+      </c>
+      <c r="D156">
+        <v>156141.2</v>
+      </c>
+      <c r="E156">
+        <v>0.003207254075157613</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>9</v>
+      </c>
+      <c r="B157">
+        <v>2005</v>
+      </c>
+      <c r="C157">
+        <v>734.646</v>
+      </c>
+      <c r="D157">
+        <v>170191.2</v>
+      </c>
+      <c r="E157">
+        <v>0.004316592162226953</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158">
+        <v>2006</v>
+      </c>
+      <c r="C158">
+        <v>893.3625000000001</v>
+      </c>
+      <c r="D158">
+        <v>184787.7</v>
+      </c>
+      <c r="E158">
+        <v>0.004834534441415744</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>9</v>
+      </c>
+      <c r="B159">
+        <v>2007</v>
+      </c>
+      <c r="C159">
+        <v>915.4981</v>
+      </c>
+      <c r="D159">
+        <v>196942.4</v>
+      </c>
+      <c r="E159">
+        <v>0.004648557649343158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>9</v>
+      </c>
+      <c r="B160">
+        <v>2008</v>
+      </c>
+      <c r="C160">
+        <v>1426.6723</v>
+      </c>
+      <c r="D160">
+        <v>187155.1</v>
+      </c>
+      <c r="E160">
+        <v>0.007622941079350762</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>9</v>
+      </c>
+      <c r="B161">
+        <v>2009</v>
+      </c>
+      <c r="C161">
+        <v>1004.5101</v>
+      </c>
+      <c r="D161">
+        <v>169407.8</v>
+      </c>
+      <c r="E161">
+        <v>0.005929538663509</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>9</v>
+      </c>
+      <c r="B162">
+        <v>2010</v>
+      </c>
+      <c r="C162">
+        <v>1610.4147</v>
+      </c>
+      <c r="D162">
+        <v>167151</v>
+      </c>
+      <c r="E162">
+        <v>0.009634490370981926</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163">
+        <v>2011</v>
+      </c>
+      <c r="C163">
+        <v>1038.525</v>
+      </c>
+      <c r="D163">
+        <v>173003.5</v>
+      </c>
+      <c r="E163">
+        <v>0.006002913235859391</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>9</v>
+      </c>
+      <c r="B164">
+        <v>2012</v>
+      </c>
+      <c r="C164">
+        <v>858.485</v>
+      </c>
+      <c r="D164">
+        <v>176519</v>
+      </c>
+      <c r="E164">
+        <v>0.004863414136721826</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>9</v>
+      </c>
+      <c r="B165">
+        <v>2013</v>
+      </c>
+      <c r="C165">
+        <v>1148.614</v>
+      </c>
+      <c r="D165">
+        <v>182697.2</v>
+      </c>
+      <c r="E165">
+        <v>0.00628698195703054</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166">
+        <v>2014</v>
+      </c>
+      <c r="C166">
+        <v>927.1202000000001</v>
+      </c>
+      <c r="D166">
+        <v>200397.6</v>
+      </c>
+      <c r="E166">
+        <v>0.004626403709425662</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167">
+        <v>2015</v>
+      </c>
+      <c r="C167">
+        <v>865.2609</v>
+      </c>
+      <c r="D167">
+        <v>272125.4</v>
+      </c>
+      <c r="E167">
+        <v>0.003179640342283374</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168">
+        <v>2016</v>
+      </c>
+      <c r="C168">
+        <v>808.7341</v>
+      </c>
+      <c r="D168">
+        <v>275805.5</v>
+      </c>
+      <c r="E168">
+        <v>0.002932262409560361</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>9</v>
+      </c>
+      <c r="B169">
+        <v>2017</v>
+      </c>
+      <c r="C169">
+        <v>977.3652</v>
+      </c>
+      <c r="D169">
+        <v>308232.9</v>
+      </c>
+      <c r="E169">
+        <v>0.00317086592638229</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>9</v>
+      </c>
+      <c r="B170">
+        <v>2018</v>
+      </c>
+      <c r="C170">
+        <v>883.5659000000001</v>
+      </c>
+      <c r="D170">
+        <v>334940.2</v>
+      </c>
+      <c r="E170">
+        <v>0.002637981048557325</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>9</v>
+      </c>
+      <c r="B171">
+        <v>2019</v>
+      </c>
+      <c r="C171">
+        <v>1207.4217</v>
+      </c>
+      <c r="D171">
+        <v>363591</v>
+      </c>
+      <c r="E171">
+        <v>0.003320823947787487</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>9</v>
+      </c>
+      <c r="B172">
+        <v>2020</v>
+      </c>
+      <c r="C172">
+        <v>1696.3895</v>
+      </c>
+      <c r="D172">
+        <v>380700.9</v>
+      </c>
+      <c r="E172">
+        <v>0.004455963986426089</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173">
+        <v>2021</v>
+      </c>
+      <c r="C173">
+        <v>3216.4458</v>
+      </c>
+      <c r="D173">
+        <v>448469.2</v>
+      </c>
+      <c r="E173">
+        <v>0.0071720550708945</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>9</v>
+      </c>
+      <c r="B174">
+        <v>2022</v>
+      </c>
+      <c r="C174">
+        <v>1781.6976</v>
+      </c>
+      <c r="D174">
+        <v>523248.2</v>
+      </c>
+      <c r="E174">
+        <v>0.003405071627575594</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>9</v>
+      </c>
+      <c r="B175">
+        <v>2023</v>
+      </c>
+      <c r="C175">
+        <v>1932.176</v>
+      </c>
+      <c r="D175">
+        <v>520792.2</v>
+      </c>
+      <c r="E175">
+        <v>0.003710070926561496</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>9</v>
+      </c>
+      <c r="B176">
+        <v>2024</v>
+      </c>
+      <c r="C176">
+        <v>2064.1842</v>
+      </c>
+      <c r="D176">
+        <v>561940.5</v>
+      </c>
+      <c r="E176">
+        <v>0.003673314523512721</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>10</v>
+      </c>
+      <c r="B177">
+        <v>2000</v>
+      </c>
+      <c r="C177">
+        <v>4903.3041373</v>
+      </c>
+      <c r="D177">
+        <v>1244744.2</v>
+      </c>
+      <c r="E177">
+        <v>0.003939206254023919</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
+        <v>10</v>
+      </c>
+      <c r="B178">
+        <v>2001</v>
+      </c>
+      <c r="C178">
+        <v>5324.4168975</v>
+      </c>
+      <c r="D178">
+        <v>1308623.1</v>
+      </c>
+      <c r="E178">
+        <v>0.004068716880742821</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>10</v>
+      </c>
+      <c r="B179">
+        <v>2002</v>
+      </c>
+      <c r="C179">
+        <v>6399.6903</v>
+      </c>
+      <c r="D179">
+        <v>1355522.3</v>
+      </c>
+      <c r="E179">
+        <v>0.004721198832361518</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
+        <v>10</v>
+      </c>
+      <c r="B180">
+        <v>2003</v>
+      </c>
+      <c r="C180">
+        <v>6107.8759</v>
+      </c>
+      <c r="D180">
+        <v>1399386</v>
+      </c>
+      <c r="E180">
+        <v>0.004364682725138025</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
+        <v>10</v>
+      </c>
+      <c r="B181">
+        <v>2004</v>
+      </c>
+      <c r="C181">
+        <v>5863.926899999999</v>
+      </c>
+      <c r="D181">
+        <v>1457356.2</v>
+      </c>
+      <c r="E181">
+        <v>0.004023674445547355</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
+        <v>10</v>
+      </c>
+      <c r="B182">
+        <v>2005</v>
+      </c>
+      <c r="C182">
+        <v>5940.1968</v>
+      </c>
+      <c r="D182">
+        <v>1499073.1</v>
+      </c>
+      <c r="E182">
+        <v>0.003962579810150685</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
+        <v>10</v>
+      </c>
+      <c r="B183">
+        <v>2006</v>
+      </c>
+      <c r="C183">
+        <v>6326.2766</v>
+      </c>
+      <c r="D183">
+        <v>1559864.2</v>
+      </c>
+      <c r="E183">
+        <v>0.004055658563097993</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
+        <v>10</v>
+      </c>
+      <c r="B184">
+        <v>2007</v>
+      </c>
+      <c r="C184">
+        <v>5355.4114</v>
+      </c>
+      <c r="D184">
+        <v>1621714.5</v>
+      </c>
+      <c r="E184">
+        <v>0.003302314556600437</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
+        <v>10</v>
+      </c>
+      <c r="B185">
+        <v>2008</v>
+      </c>
+      <c r="C185">
+        <v>5363.1075</v>
+      </c>
+      <c r="D185">
+        <v>1643718.8</v>
+      </c>
+      <c r="E185">
+        <v>0.003262788927157127</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
+        <v>10</v>
+      </c>
+      <c r="B186">
+        <v>2009</v>
+      </c>
+      <c r="C186">
+        <v>4799.289400000001</v>
+      </c>
+      <c r="D186">
+        <v>1584106.8</v>
+      </c>
+      <c r="E186">
+        <v>0.003029650147325925</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>10</v>
+      </c>
+      <c r="B187">
+        <v>2010</v>
+      </c>
+      <c r="C187">
+        <v>3802.3499</v>
+      </c>
+      <c r="D187">
+        <v>1617944.7</v>
+      </c>
+      <c r="E187">
+        <v>0.002350111162637388</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>10</v>
+      </c>
+      <c r="B188">
+        <v>2011</v>
+      </c>
+      <c r="C188">
+        <v>3613.27</v>
+      </c>
+      <c r="D188">
+        <v>1657362.2</v>
+      </c>
+      <c r="E188">
+        <v>0.002180132984811648</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>10</v>
+      </c>
+      <c r="B189">
+        <v>2012</v>
+      </c>
+      <c r="C189">
+        <v>4182.0394</v>
+      </c>
+      <c r="D189">
+        <v>1632898.5</v>
+      </c>
+      <c r="E189">
+        <v>0.002561114117013397</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
+        <v>10</v>
+      </c>
+      <c r="B190">
+        <v>2013</v>
+      </c>
+      <c r="C190">
+        <v>3369.0106</v>
+      </c>
+      <c r="D190">
+        <v>1621260.7</v>
+      </c>
+      <c r="E190">
+        <v>0.002078019037900567</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
+        <v>10</v>
+      </c>
+      <c r="B191">
+        <v>2014</v>
+      </c>
+      <c r="C191">
+        <v>3581.021</v>
+      </c>
+      <c r="D191">
+        <v>1635870.7</v>
+      </c>
+      <c r="E191">
+        <v>0.002189061152571533</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
+        <v>10</v>
+      </c>
+      <c r="B192">
+        <v>2015</v>
+      </c>
+      <c r="C192">
+        <v>3730.8358</v>
+      </c>
+      <c r="D192">
+        <v>1663277.7</v>
+      </c>
+      <c r="E192">
+        <v>0.002243062478382293</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
+        <v>10</v>
+      </c>
+      <c r="B193">
+        <v>2016</v>
+      </c>
+      <c r="C193">
+        <v>3832.8342</v>
+      </c>
+      <c r="D193">
+        <v>1704856.7</v>
+      </c>
+      <c r="E193">
+        <v>0.002248185551313492</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
+        <v>10</v>
+      </c>
+      <c r="B194">
+        <v>2017</v>
+      </c>
+      <c r="C194">
+        <v>4924.8627</v>
+      </c>
+      <c r="D194">
+        <v>1744493</v>
+      </c>
+      <c r="E194">
+        <v>0.002823091121603812</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
+        <v>10</v>
+      </c>
+      <c r="B195">
+        <v>2018</v>
+      </c>
+      <c r="C195">
+        <v>7420.222000000001</v>
+      </c>
+      <c r="D195">
+        <v>1777744.4</v>
+      </c>
+      <c r="E195">
+        <v>0.0041739532409721</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
+        <v>10</v>
+      </c>
+      <c r="B196">
+        <v>2019</v>
+      </c>
+      <c r="C196">
+        <v>7642.2953</v>
+      </c>
+      <c r="D196">
+        <v>1804066.8</v>
+      </c>
+      <c r="E196">
+        <v>0.004236148739059995</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
+        <v>10</v>
+      </c>
+      <c r="B197">
+        <v>2020</v>
+      </c>
+      <c r="C197">
+        <v>32787.1087</v>
+      </c>
+      <c r="D197">
+        <v>1670011.9</v>
+      </c>
+      <c r="E197">
+        <v>0.01963285932273896</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
+        <v>10</v>
+      </c>
+      <c r="B198">
+        <v>2021</v>
+      </c>
+      <c r="C198">
+        <v>37815.8946</v>
+      </c>
+      <c r="D198">
+        <v>1842507.4</v>
+      </c>
+      <c r="E198">
+        <v>0.02052414801699032</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
+        <v>10</v>
+      </c>
+      <c r="B199">
+        <v>2022</v>
+      </c>
+      <c r="C199">
+        <v>27645.5703</v>
+      </c>
+      <c r="D199">
+        <v>1998072.6</v>
+      </c>
+      <c r="E199">
+        <v>0.01383611901789755</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
+        <v>10</v>
+      </c>
+      <c r="B200">
+        <v>2023</v>
+      </c>
+      <c r="C200">
+        <v>22525.8228</v>
+      </c>
+      <c r="D200">
+        <v>2142744.4</v>
+      </c>
+      <c r="E200">
+        <v>0.01051260374312494</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
+        <v>10</v>
+      </c>
+      <c r="B201">
+        <v>2024</v>
+      </c>
+      <c r="C201">
+        <v>17834.9809</v>
+      </c>
+      <c r="D201">
+        <v>2202031.2</v>
+      </c>
+      <c r="E201">
+        <v>0.008099331608017178</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
+        <v>11</v>
+      </c>
+      <c r="B202">
+        <v>2000</v>
+      </c>
+      <c r="C202">
+        <v>936.7126508</v>
+      </c>
+      <c r="D202">
+        <v>452191</v>
+      </c>
+      <c r="E202">
+        <v>0.002071497775939813</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
+        <v>11</v>
+      </c>
+      <c r="B203">
+        <v>2001</v>
+      </c>
+      <c r="C203">
+        <v>850.3461693</v>
+      </c>
+      <c r="D203">
+        <v>482941</v>
+      </c>
+      <c r="E203">
+        <v>0.001760766158392019</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
+        <v>11</v>
+      </c>
+      <c r="B204">
+        <v>2002</v>
+      </c>
+      <c r="C204">
+        <v>1623.7954</v>
+      </c>
+      <c r="D204">
+        <v>502901</v>
+      </c>
+      <c r="E204">
+        <v>0.00322885697184933</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
+        <v>11</v>
+      </c>
+      <c r="B205">
+        <v>2003</v>
+      </c>
+      <c r="C205">
+        <v>1615.5107</v>
+      </c>
+      <c r="D205">
+        <v>514901</v>
+      </c>
+      <c r="E205">
+        <v>0.003137517114940542</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
+        <v>11</v>
+      </c>
+      <c r="B206">
+        <v>2004</v>
+      </c>
+      <c r="C206">
+        <v>1468.2381</v>
+      </c>
+      <c r="D206">
+        <v>531573</v>
+      </c>
+      <c r="E206">
+        <v>0.002762062971595623</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
+        <v>11</v>
+      </c>
+      <c r="B207">
+        <v>2005</v>
+      </c>
+      <c r="C207">
+        <v>1546.5347</v>
+      </c>
+      <c r="D207">
+        <v>553122</v>
+      </c>
+      <c r="E207">
+        <v>0.002796010102653664</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
+        <v>11</v>
+      </c>
+      <c r="B208">
+        <v>2006</v>
+      </c>
+      <c r="C208">
+        <v>1757.3062</v>
+      </c>
+      <c r="D208">
+        <v>587444</v>
+      </c>
+      <c r="E208">
+        <v>0.002991444631318049</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
+        <v>11</v>
+      </c>
+      <c r="B209">
+        <v>2007</v>
+      </c>
+      <c r="C209">
+        <v>1825.1242</v>
+      </c>
+      <c r="D209">
+        <v>622775</v>
+      </c>
+      <c r="E209">
+        <v>0.002930631769097989</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
+        <v>11</v>
+      </c>
+      <c r="B210">
+        <v>2008</v>
+      </c>
+      <c r="C210">
+        <v>1924.4716</v>
+      </c>
+      <c r="D210">
+        <v>651299</v>
+      </c>
+      <c r="E210">
+        <v>0.002954820443452239</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
+        <v>11</v>
+      </c>
+      <c r="B211">
+        <v>2009</v>
+      </c>
+      <c r="C211">
+        <v>2119.3592</v>
+      </c>
+      <c r="D211">
+        <v>630173</v>
+      </c>
+      <c r="E211">
+        <v>0.003363138693660312</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" t="s">
+        <v>11</v>
+      </c>
+      <c r="B212">
+        <v>2010</v>
+      </c>
+      <c r="C212">
+        <v>2431.1165</v>
+      </c>
+      <c r="D212">
+        <v>643022</v>
+      </c>
+      <c r="E212">
+        <v>0.003780767221028207</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" t="s">
+        <v>11</v>
+      </c>
+      <c r="B213">
+        <v>2011</v>
+      </c>
+      <c r="C213">
+        <v>2484.234</v>
+      </c>
+      <c r="D213">
+        <v>656013</v>
+      </c>
+      <c r="E213">
+        <v>0.003786867028549739</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="s">
+        <v>11</v>
+      </c>
+      <c r="B214">
+        <v>2012</v>
+      </c>
+      <c r="C214">
+        <v>2256.3805</v>
+      </c>
+      <c r="D214">
+        <v>658232</v>
+      </c>
+      <c r="E214">
+        <v>0.00342794106029485</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="s">
+        <v>11</v>
+      </c>
+      <c r="B215">
+        <v>2013</v>
+      </c>
+      <c r="C215">
+        <v>2078.7249</v>
+      </c>
+      <c r="D215">
+        <v>665567</v>
+      </c>
+      <c r="E215">
+        <v>0.003123239132949801</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="s">
+        <v>11</v>
+      </c>
+      <c r="B216">
+        <v>2014</v>
+      </c>
+      <c r="C216">
+        <v>2092.8313</v>
+      </c>
+      <c r="D216">
+        <v>678627</v>
+      </c>
+      <c r="E216">
+        <v>0.003083919885297814</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="s">
+        <v>11</v>
+      </c>
+      <c r="B217">
+        <v>2015</v>
+      </c>
+      <c r="C217">
+        <v>2107.5653</v>
+      </c>
+      <c r="D217">
+        <v>699175</v>
+      </c>
+      <c r="E217">
+        <v>0.003014360210247792</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" t="s">
+        <v>11</v>
+      </c>
+      <c r="B218">
+        <v>2016</v>
+      </c>
+      <c r="C218">
+        <v>2462.0394</v>
+      </c>
+      <c r="D218">
+        <v>720175</v>
+      </c>
+      <c r="E218">
+        <v>0.003418668240358246</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" t="s">
+        <v>11</v>
+      </c>
+      <c r="B219">
+        <v>2017</v>
+      </c>
+      <c r="C219">
+        <v>2345.7005</v>
+      </c>
+      <c r="D219">
+        <v>750861</v>
+      </c>
+      <c r="E219">
+        <v>0.003124014298252273</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" t="s">
+        <v>11</v>
+      </c>
+      <c r="B220">
+        <v>2018</v>
+      </c>
+      <c r="C220">
+        <v>2620.9465</v>
+      </c>
+      <c r="D220">
+        <v>787273</v>
+      </c>
+      <c r="E220">
+        <v>0.00332914567119665</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" t="s">
+        <v>11</v>
+      </c>
+      <c r="B221">
+        <v>2019</v>
+      </c>
+      <c r="C221">
+        <v>2515.7685</v>
+      </c>
+      <c r="D221">
+        <v>829767</v>
+      </c>
+      <c r="E221">
+        <v>0.003031897508577709</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" t="s">
+        <v>11</v>
+      </c>
+      <c r="B222">
+        <v>2020</v>
+      </c>
+      <c r="C222">
+        <v>5284.7155</v>
+      </c>
+      <c r="D222">
+        <v>816463</v>
+      </c>
+      <c r="E222">
+        <v>0.006472694414811205</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" t="s">
+        <v>11</v>
+      </c>
+      <c r="B223">
+        <v>2021</v>
+      </c>
+      <c r="C223">
+        <v>11871.601</v>
+      </c>
+      <c r="D223">
+        <v>891550</v>
+      </c>
+      <c r="E223">
+        <v>0.01331568728618698</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" t="s">
+        <v>11</v>
+      </c>
+      <c r="B224">
+        <v>2022</v>
+      </c>
+      <c r="C224">
+        <v>8202.7778</v>
+      </c>
+      <c r="D224">
+        <v>993820</v>
+      </c>
+      <c r="E224">
+        <v>0.008253786198708016</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" t="s">
+        <v>11</v>
+      </c>
+      <c r="B225">
+        <v>2023</v>
+      </c>
+      <c r="C225">
+        <v>5211.6044</v>
+      </c>
+      <c r="D225">
+        <v>1050133</v>
+      </c>
+      <c r="E225">
+        <v>0.004962804140047023</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" t="s">
+        <v>11</v>
+      </c>
+      <c r="B226">
+        <v>2024</v>
+      </c>
+      <c r="C226">
+        <v>4766.668900000001</v>
+      </c>
+      <c r="D226">
+        <v>1115252</v>
+      </c>
+      <c r="E226">
+        <v>0.004274073393277933</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227">
+        <v>2000</v>
+      </c>
+      <c r="C227">
+        <v>1703.4771739</v>
+      </c>
+      <c r="D227">
+        <v>128414.4</v>
+      </c>
+      <c r="E227">
+        <v>0.01326546846693206</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228">
+        <v>2001</v>
+      </c>
+      <c r="C228">
+        <v>2937.3592775</v>
+      </c>
+      <c r="D228">
+        <v>135775</v>
+      </c>
+      <c r="E228">
+        <v>0.02163402156140674</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" t="s">
+        <v>12</v>
+      </c>
+      <c r="B229">
+        <v>2002</v>
+      </c>
+      <c r="C229">
+        <v>2916.1032</v>
+      </c>
+      <c r="D229">
+        <v>142554.3</v>
+      </c>
+      <c r="E229">
+        <v>0.02045608725938116</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" t="s">
+        <v>12</v>
+      </c>
+      <c r="B230">
+        <v>2003</v>
+      </c>
+      <c r="C230">
+        <v>3134.3583</v>
+      </c>
+      <c r="D230">
+        <v>146067.9</v>
+      </c>
+      <c r="E230">
+        <v>0.02145822798849029</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" t="s">
+        <v>12</v>
+      </c>
+      <c r="B231">
+        <v>2004</v>
+      </c>
+      <c r="C231">
+        <v>2129.0936</v>
+      </c>
+      <c r="D231">
+        <v>152248.4</v>
+      </c>
+      <c r="E231">
+        <v>0.01398434137895702</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" t="s">
+        <v>12</v>
+      </c>
+      <c r="B232">
+        <v>2005</v>
+      </c>
+      <c r="C232">
+        <v>1381.753</v>
+      </c>
+      <c r="D232">
+        <v>158552.7</v>
+      </c>
+      <c r="E232">
+        <v>0.008714786944656255</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" t="s">
+        <v>12</v>
+      </c>
+      <c r="B233">
+        <v>2006</v>
+      </c>
+      <c r="C233">
+        <v>1432.7325</v>
+      </c>
+      <c r="D233">
+        <v>166260.5</v>
+      </c>
+      <c r="E233">
+        <v>0.00861739559306029</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" t="s">
+        <v>12</v>
+      </c>
+      <c r="B234">
+        <v>2007</v>
+      </c>
+      <c r="C234">
+        <v>2149.9069</v>
+      </c>
+      <c r="D234">
+        <v>175483.4</v>
+      </c>
+      <c r="E234">
+        <v>0.01225134058264201</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" t="s">
+        <v>12</v>
+      </c>
+      <c r="B235">
+        <v>2008</v>
+      </c>
+      <c r="C235">
+        <v>1582.0714</v>
+      </c>
+      <c r="D235">
+        <v>179102.8</v>
+      </c>
+      <c r="E235">
+        <v>0.008833314722047897</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236">
+        <v>2009</v>
+      </c>
+      <c r="C236">
+        <v>1633.527</v>
+      </c>
+      <c r="D236">
+        <v>175416.4</v>
+      </c>
+      <c r="E236">
+        <v>0.009312282089930018</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" t="s">
+        <v>12</v>
+      </c>
+      <c r="B237">
+        <v>2010</v>
+      </c>
+      <c r="C237">
+        <v>2252.6978</v>
+      </c>
+      <c r="D237">
+        <v>179860.4</v>
+      </c>
+      <c r="E237">
+        <v>0.01252470137951433</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" t="s">
+        <v>12</v>
+      </c>
+      <c r="B238">
+        <v>2011</v>
+      </c>
+      <c r="C238">
+        <v>1747.6994</v>
+      </c>
+      <c r="D238">
+        <v>176318</v>
+      </c>
+      <c r="E238">
+        <v>0.009912200682857111</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" t="s">
+        <v>12</v>
+      </c>
+      <c r="B239">
+        <v>2012</v>
+      </c>
+      <c r="C239">
+        <v>1116.1075</v>
+      </c>
+      <c r="D239">
+        <v>168538.8</v>
+      </c>
+      <c r="E239">
+        <v>0.006622258494779838</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" t="s">
+        <v>12</v>
+      </c>
+      <c r="B240">
+        <v>2013</v>
+      </c>
+      <c r="C240">
+        <v>814.386</v>
+      </c>
+      <c r="D240">
+        <v>170675.6</v>
+      </c>
+      <c r="E240">
+        <v>0.004771543208285191</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" t="s">
+        <v>12</v>
+      </c>
+      <c r="B241">
+        <v>2014</v>
+      </c>
+      <c r="C241">
+        <v>718.399</v>
+      </c>
+      <c r="D241">
+        <v>173186.7</v>
+      </c>
+      <c r="E241">
+        <v>0.004148118764316197</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242">
+        <v>2015</v>
+      </c>
+      <c r="C242">
+        <v>917.0309999999999</v>
+      </c>
+      <c r="D242">
+        <v>179392.7</v>
+      </c>
+      <c r="E242">
+        <v>0.005111863526219293</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" t="s">
+        <v>12</v>
+      </c>
+      <c r="B243">
+        <v>2016</v>
+      </c>
+      <c r="C243">
+        <v>735.0174</v>
+      </c>
+      <c r="D243">
+        <v>186380.7</v>
+      </c>
+      <c r="E243">
+        <v>0.003943634721835469</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="s">
+        <v>12</v>
+      </c>
+      <c r="B244">
+        <v>2017</v>
+      </c>
+      <c r="C244">
+        <v>1061.5442</v>
+      </c>
+      <c r="D244">
+        <v>195509.1</v>
+      </c>
+      <c r="E244">
+        <v>0.005429640870936441</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
+        <v>12</v>
+      </c>
+      <c r="B245">
+        <v>2018</v>
+      </c>
+      <c r="C245">
+        <v>1173.434</v>
+      </c>
+      <c r="D245">
+        <v>204997.6</v>
+      </c>
+      <c r="E245">
+        <v>0.005724135306949935</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="s">
+        <v>12</v>
+      </c>
+      <c r="B246">
+        <v>2019</v>
+      </c>
+      <c r="C246">
+        <v>1132.739</v>
+      </c>
+      <c r="D246">
+        <v>214489.9</v>
+      </c>
+      <c r="E246">
+        <v>0.0052810831652213</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="s">
+        <v>12</v>
+      </c>
+      <c r="B247">
+        <v>2020</v>
+      </c>
+      <c r="C247">
+        <v>3218.5303</v>
+      </c>
+      <c r="D247">
+        <v>201032.7</v>
+      </c>
+      <c r="E247">
+        <v>0.0160099839478851</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" t="s">
+        <v>12</v>
+      </c>
+      <c r="B248">
+        <v>2021</v>
+      </c>
+      <c r="C248">
+        <v>2292.7581</v>
+      </c>
+      <c r="D248">
+        <v>216493.7</v>
+      </c>
+      <c r="E248">
+        <v>0.01059041487119487</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" t="s">
+        <v>12</v>
+      </c>
+      <c r="B249">
+        <v>2022</v>
+      </c>
+      <c r="C249">
+        <v>1568.9854</v>
+      </c>
+      <c r="D249">
+        <v>243957.1</v>
+      </c>
+      <c r="E249">
+        <v>0.006431398799215108</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" t="s">
+        <v>12</v>
+      </c>
+      <c r="B250">
+        <v>2023</v>
+      </c>
+      <c r="C250">
+        <v>1584.4747</v>
+      </c>
+      <c r="D250">
+        <v>270352.6</v>
+      </c>
+      <c r="E250">
+        <v>0.005860771081913028</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" t="s">
+        <v>12</v>
+      </c>
+      <c r="B251">
+        <v>2024</v>
+      </c>
+      <c r="C251">
+        <v>1079.4098</v>
+      </c>
+      <c r="D251">
+        <v>289784.3</v>
+      </c>
+      <c r="E251">
+        <v>0.003724873293687753</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C111"/>
@@ -83090,10 +87377,10 @@
         <v>143</v>
       </c>
       <c r="C108">
-        <v>12593.318359375</v>
+        <v>12689.8203125</v>
       </c>
       <c r="D108">
-        <v>-0.1233771635146863</v>
+        <v>-0.1157434260261486</v>
       </c>
     </row>
   </sheetData>
@@ -84609,10 +88896,10 @@
         <v>143</v>
       </c>
       <c r="C108">
-        <v>4976.740234375</v>
+        <v>4978.77978515625</v>
       </c>
       <c r="D108">
-        <v>0.03086074893546682</v>
+        <v>0.03127048158745942</v>
       </c>
     </row>
   </sheetData>
@@ -92588,9 +96875,6 @@
       <c r="E175">
         <v>555056951</v>
       </c>
-      <c r="F175">
-        <v>6894360</v>
-      </c>
       <c r="G175">
         <v>14868010</v>
       </c>
@@ -92608,7 +96892,7 @@
       </c>
       <c r="L175">
         <f>SUM(C175:J175)/K175</f>
-        <v>0.002144391398616143</v>
+        <v>0.0021254894796605478</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -92627,9 +96911,6 @@
       <c r="E176">
         <v>491049223</v>
       </c>
-      <c r="F176">
-        <v>835423</v>
-      </c>
       <c r="G176">
         <v>19029410</v>
       </c>
@@ -92647,7 +96928,7 @@
       </c>
       <c r="L176">
         <f>SUM(C176:J176)/K176</f>
-        <v>0.0017493858411826825</v>
+        <v>0.0017471219176536802</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -92666,9 +96947,6 @@
       <c r="E177">
         <v>363989822</v>
       </c>
-      <c r="F177">
-        <v>146363</v>
-      </c>
       <c r="G177">
         <v>11344061</v>
       </c>
@@ -92686,7 +96964,7 @@
       </c>
       <c r="L177">
         <f>SUM(C177:J177)/K177</f>
-        <v>0.0017428884368764193</v>
+        <v>0.0017423867351796906</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -92705,9 +96983,6 @@
       <c r="E178">
         <v>388558575</v>
       </c>
-      <c r="F178">
-        <v>438542</v>
-      </c>
       <c r="G178">
         <v>357522716</v>
       </c>
@@ -92725,7 +97000,7 @@
       </c>
       <c r="L178">
         <f>SUM(C178:J178)/K178</f>
-        <v>0.002760368110462393</v>
+        <v>0.002759068369963979</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -92744,9 +97019,6 @@
       <c r="E179">
         <v>315464338</v>
       </c>
-      <c r="F179">
-        <v>967748</v>
-      </c>
       <c r="G179">
         <v>694238601</v>
       </c>
@@ -92764,7 +97036,7 @@
       </c>
       <c r="L179">
         <f>SUM(C179:J179)/K179</f>
-        <v>0.003524093118364491</v>
+        <v>0.0035215186620328556</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -92783,9 +97055,6 @@
       <c r="E180">
         <v>234192376</v>
       </c>
-      <c r="F180">
-        <v>403358</v>
-      </c>
       <c r="G180">
         <v>50941701</v>
       </c>
@@ -92803,7 +97072,7 @@
       </c>
       <c r="L180">
         <f>SUM(C180:J180)/K180</f>
-        <v>0.0013944725099856092</v>
+        <v>0.0013934387413724269</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -92822,9 +97091,6 @@
       <c r="E181">
         <v>243462192</v>
       </c>
-      <c r="F181">
-        <v>544052</v>
-      </c>
       <c r="G181">
         <v>38239093</v>
       </c>
@@ -92842,7 +97108,7 @@
       </c>
       <c r="L181">
         <f>SUM(C181:J181)/K181</f>
-        <v>0.0015198430359125198</v>
+        <v>0.0015184488622590933</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -92861,9 +97127,6 @@
       <c r="E182">
         <v>229425096</v>
       </c>
-      <c r="F182">
-        <v>368877</v>
-      </c>
       <c r="G182">
         <v>51741911</v>
       </c>
@@ -92881,7 +97144,7 @@
       </c>
       <c r="L182">
         <f>SUM(C182:J182)/K182</f>
-        <v>0.001502312814204478</v>
+        <v>0.001501388010089781</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -92900,9 +97163,6 @@
       <c r="E183">
         <v>239704470</v>
       </c>
-      <c r="F183">
-        <v>2114906</v>
-      </c>
       <c r="G183">
         <v>76968357</v>
       </c>
@@ -92920,7 +97180,7 @@
       </c>
       <c r="L183">
         <f>SUM(C183:J183)/K183</f>
-        <v>0.0015534997201821193</v>
+        <v>0.001548370079876957</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -92939,9 +97199,6 @@
       <c r="E184">
         <v>256835600</v>
       </c>
-      <c r="F184">
-        <v>1300353</v>
-      </c>
       <c r="G184">
         <v>168396189</v>
       </c>
@@ -92959,7 +97216,7 @@
       </c>
       <c r="L184">
         <f>SUM(C184:J184)/K184</f>
-        <v>0.001718363340449374</v>
+        <v>0.0017152469975612913</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -92978,9 +97235,6 @@
       <c r="E185">
         <v>275704101</v>
       </c>
-      <c r="F185">
-        <v>1195674</v>
-      </c>
       <c r="G185">
         <v>77434488</v>
       </c>
@@ -92998,7 +97252,7 @@
       </c>
       <c r="L185">
         <f>SUM(C185:J185)/K185</f>
-        <v>0.0014495252860558358</v>
+        <v>0.0014468630800577333</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -93017,9 +97271,6 @@
       <c r="E186">
         <v>348371204</v>
       </c>
-      <c r="F186">
-        <v>1406268</v>
-      </c>
       <c r="G186">
         <v>80278042</v>
       </c>
@@ -93037,7 +97288,7 @@
       </c>
       <c r="L186">
         <f>SUM(C186:J186)/K186</f>
-        <v>0.001452138107130523</v>
+        <v>0.0014491159898051198</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -93056,9 +97307,6 @@
       <c r="E187">
         <v>432249195</v>
       </c>
-      <c r="F187">
-        <v>1329323</v>
-      </c>
       <c r="G187">
         <v>81621699</v>
       </c>
@@ -93076,7 +97324,7 @@
       </c>
       <c r="L187">
         <f>SUM(C187:J187)/K187</f>
-        <v>0.0014477621546120719</v>
+        <v>0.0014449947616008254</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -93095,9 +97343,6 @@
       <c r="E188">
         <v>410791828</v>
       </c>
-      <c r="F188">
-        <v>3195417</v>
-      </c>
       <c r="G188">
         <v>88385381</v>
       </c>
@@ -93115,7 +97360,7 @@
       </c>
       <c r="L188">
         <f>SUM(C188:J188)/K188</f>
-        <v>0.0016935692720274557</v>
+        <v>0.0016862523806117978</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -93134,9 +97379,6 @@
       <c r="E189">
         <v>412596324</v>
       </c>
-      <c r="F189">
-        <v>3152947</v>
-      </c>
       <c r="G189">
         <v>83264022</v>
       </c>
@@ -93154,7 +97396,7 @@
       </c>
       <c r="L189">
         <f>SUM(C189:J189)/K189</f>
-        <v>0.0014517224934586452</v>
+        <v>0.0014456681117781679</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -93173,9 +97415,6 @@
       <c r="E190">
         <v>412912553</v>
       </c>
-      <c r="F190">
-        <v>1958355</v>
-      </c>
       <c r="G190">
         <v>93515822</v>
       </c>
@@ -93193,7 +97432,7 @@
       </c>
       <c r="L190">
         <f>SUM(C190:J190)/K190</f>
-        <v>0.0013335338757883683</v>
+        <v>0.0013304063597103831</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -93212,9 +97451,6 @@
       <c r="E191">
         <v>384053532</v>
       </c>
-      <c r="F191">
-        <v>9860127</v>
-      </c>
       <c r="G191">
         <v>174401481</v>
       </c>
@@ -93232,7 +97468,7 @@
       </c>
       <c r="L191">
         <f>SUM(C191:J191)/K191</f>
-        <v>0.0013749677398369557</v>
+        <v>0.0013592154736887776</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -93251,9 +97487,6 @@
       <c r="E192">
         <v>339160901</v>
       </c>
-      <c r="F192">
-        <v>5684683</v>
-      </c>
       <c r="G192">
         <v>145937813</v>
       </c>
@@ -93271,7 +97504,7 @@
       </c>
       <c r="L192">
         <f>SUM(C192:J192)/K192</f>
-        <v>0.0012750174822534505</v>
+        <v>0.0012658870303831995</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -93290,9 +97523,6 @@
       <c r="E193">
         <v>334151250</v>
       </c>
-      <c r="F193">
-        <v>19473695</v>
-      </c>
       <c r="G193">
         <v>63548964</v>
       </c>
@@ -93310,7 +97540,7 @@
       </c>
       <c r="L193">
         <f>SUM(C193:J193)/K193</f>
-        <v>0.001287675995910038</v>
+        <v>0.001257397528805886</v>
       </c>
     </row>
     <row r="194" spans="1:12">

--- a/ai_data.xlsx
+++ b/ai_data.xlsx
@@ -71406,10 +71406,10 @@
         <v>144</v>
       </c>
       <c r="D109">
-        <v>1128.329956054688</v>
+        <v>1124.359985351562</v>
       </c>
       <c r="E109">
-        <v>0.01197388784542648</v>
+        <v>0.008449235171196041</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -73239,10 +73239,10 @@
         <v>144</v>
       </c>
       <c r="D217">
-        <v>25449.189453125</v>
+        <v>25248.630859375</v>
       </c>
       <c r="E217">
-        <v>0.009872064447602439</v>
+        <v>0.00196010141858317</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -75072,10 +75072,10 @@
         <v>144</v>
       </c>
       <c r="D325">
-        <v>7865.06982421875</v>
+        <v>7815</v>
       </c>
       <c r="E325">
-        <v>-0.01256397858420138</v>
+        <v>-0.01895042902250393</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -76905,10 +76905,10 @@
         <v>144</v>
       </c>
       <c r="D433">
-        <v>51261</v>
+        <v>50974.16015625</v>
       </c>
       <c r="E433">
-        <v>-0.0021630478165634</v>
+        <v>-0.007774436226799344</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -78738,10 +78738,10 @@
         <v>144</v>
       </c>
       <c r="D541">
-        <v>19444.19921875</v>
+        <v>19357</v>
       </c>
       <c r="E541">
-        <v>0.0009261547095066444</v>
+        <v>-0.003568519027709576</v>
       </c>
     </row>
     <row r="542" spans="1:5">
@@ -80571,10 +80571,10 @@
         <v>144</v>
       </c>
       <c r="D649">
-        <v>5569.990234375</v>
+        <v>5527.83984375</v>
       </c>
       <c r="E649">
-        <v>-0.006454865271973615</v>
+        <v>-0.01405105173516569</v>
       </c>
     </row>
     <row r="650" spans="1:5">
@@ -82404,10 +82404,10 @@
         <v>144</v>
       </c>
       <c r="D757">
-        <v>6790.77978515625</v>
+        <v>6738.89013671875</v>
       </c>
       <c r="E757">
-        <v>-0.009558403144140993</v>
+        <v>-0.01722893807316879</v>
       </c>
     </row>
     <row r="758" spans="1:5">
@@ -84237,10 +84237,10 @@
         <v>144</v>
       </c>
       <c r="D865">
-        <v>14464.1103515625</v>
+        <v>14376.9501953125</v>
       </c>
       <c r="E865">
-        <v>-0.0006669056417120767</v>
+        <v>-0.006711095414443704</v>
       </c>
     </row>
     <row r="866" spans="1:5">
@@ -85186,10 +85186,10 @@
         <v>144</v>
       </c>
       <c r="D921">
-        <v>6440.86328125</v>
+        <v>6434.734375</v>
       </c>
       <c r="E921">
-        <v>0.002325897420894164</v>
+        <v>0.001373878434819175</v>
       </c>
     </row>
     <row r="922" spans="1:5">
@@ -89184,10 +89184,10 @@
         <v>144</v>
       </c>
       <c r="C109">
-        <v>4975.669921875</v>
+        <v>4974.419921875</v>
       </c>
       <c r="D109">
-        <v>0.01477390560185798</v>
+        <v>0.01452265158783312</v>
       </c>
     </row>
   </sheetData>
@@ -91038,10 +91038,10 @@
         <v>144</v>
       </c>
       <c r="C109">
-        <v>636.6300048828125</v>
+        <v>633.8400268554688</v>
       </c>
       <c r="D109">
-        <v>0.002736868147974653</v>
+        <v>-0.001655179586412326</v>
       </c>
       <c r="E109" t="s">
         <v>151</v>
